--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Audit_report.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Audit_report.xlsx
@@ -14,20 +14,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <t>Internal Audit Report</t>
   </si>
   <si>
+    <t>OmniOps</t>
+  </si>
+  <si>
+    <t>CONFIDENTIAL</t>
+  </si>
+  <si>
     <t>AUD-2026-03 — Business Continuity Readiness</t>
   </si>
   <si>
     <t>Organisation</t>
   </si>
   <si>
-    <t>OmniOps</t>
-  </si>
-  <si>
     <t>Engagement</t>
   </si>
   <si>
@@ -46,7 +49,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-08-17 15:43 UTC</t>
+    <t>2026-09-23 10:59 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -55,6 +58,12 @@
     <t>SUBTREE</t>
   </si>
   <si>
+    <t>Document reference</t>
+  </si>
+  <si>
+    <t>1906-20260923105957</t>
+  </si>
+  <si>
     <t>DRAFT — this engagement is Planned. Figures are provisional and the conclusion is not final.</t>
   </si>
   <si>
@@ -73,7 +82,7 @@
     <t>Lead auditor</t>
   </si>
   <si>
-    <t>Mahmoud Abdulaziz</t>
+    <t>Ibrahim Abdulaziz</t>
   </si>
   <si>
     <t>Status</t>
@@ -179,7 +188,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -191,6 +200,16 @@
       <b/>
       <color rgb="FF0B1524"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF0F7A5A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF646F85"/>
+      <sz val="9"/>
     </font>
     <font>
       <color rgb="FF646F85"/>
@@ -212,7 +231,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF0B1524"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -234,7 +253,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5F7FA"/>
+        <fgColor rgb="FF0F7A5A"/>
       </patternFill>
     </fill>
   </fills>
@@ -259,24 +278,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -633,63 +654,81 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="3" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="4" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="6"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -706,107 +745,107 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>15</v>
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>17</v>
+      <c r="A2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>19</v>
+      <c r="A3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>6</v>
+      <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
+      <c r="A5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>24</v>
+      <c r="A6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>26</v>
+      <c r="A7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>28</v>
+      <c r="A8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>30</v>
+      <c r="A9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>30</v>
+      <c r="A10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>33</v>
+      <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>33</v>
+      <c r="A12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>36</v>
+      <c r="A13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -834,56 +873,56 @@
     <col min="15" max="15" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="9" t="s">
+    <row r="1" ht="22" customHeight="1" spans="1:15" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="C1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="H1" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="I1" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="J1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="K1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="L1" s="11" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="M1" s="11" t="s">
         <v>51</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -903,23 +942,23 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
-        <v>51</v>
+    <row r="1" ht="22" customHeight="1" spans="1:4" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/grc_wisdom_api/scripts/verify/_tmp_reports/Audit_report.xlsx
+++ b/grc_wisdom_api/scripts/verify/_tmp_reports/Audit_report.xlsx
@@ -49,7 +49,7 @@
     <t>Generated at</t>
   </si>
   <si>
-    <t>2026-09-23 10:59 UTC</t>
+    <t>2026-09-24 22:36 UTC</t>
   </si>
   <si>
     <t>Visibility</t>
@@ -61,7 +61,7 @@
     <t>Document reference</t>
   </si>
   <si>
-    <t>1906-20260923105957</t>
+    <t>B7C7-20260924223633</t>
   </si>
   <si>
     <t>DRAFT — this engagement is Planned. Figures are provisional and the conclusion is not final.</t>
@@ -82,7 +82,7 @@
     <t>Lead auditor</t>
   </si>
   <si>
-    <t>Ibrahim Abdulaziz</t>
+    <t>Alaa Tamimi</t>
   </si>
   <si>
     <t>Status</t>
